--- a/Excel001 (13) - Copy.xlsx
+++ b/Excel001 (13) - Copy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work_LinhLT\Contrack_new_version\ver 5.0.1\01.New Function\02.Envidence\File test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thuylinh.le\OneDrive - 株式会社ベリサーブ\Desktop\Contrack\5.0.1\6944_Envidence\New_L_project015 39\branches041\5.0.0_Github_7351_7352_repo01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D68285-9CD8-4A8A-A5C6-402AC25D4DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C96A86-4DCF-4475-A416-4F77D7A6E936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="0" windowWidth="14400" windowHeight="7280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>A01</t>
   </si>
   <si>
     <t>K</t>
+  </si>
+  <si>
+    <t>cccc</t>
   </si>
 </sst>
 </file>
@@ -348,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -359,6 +362,11 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
